--- a/data_extactor/batch_10_fa/trimmed/batch_0028_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0028_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نگارش | شنیدن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
+          <t>نگارش | گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>شیمی | آموزش و پرورش | مهندسی و فناوری | حقوق و امور دولتی | ایمنی و امنیت عمومی | مدیریت و امور اداری</t>
+          <t>شیمی | آموزش و پرورش | مهندسی و فناوری | قانون و دولت | ایمنی و امنیت عمومی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | دید نزدیک | درک شفاهی | بیان شفاهی | درک کتبی</t>
+          <t>حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | درک شفاهی | بیان شفاهی | درک کتبی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>بازرسان ساختمان و سازه | بازرسان انطباق با مقررات زیست‌محیطی | مهندسان محیط زیست | بازرسان و کارشناسان بررسی حریق | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معادن | تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | پزشکان طب کار و پزشکی پیشگیری</t>
+          <t>بازرسان ساخت‌وساز و ساختمان | بازرسان رعایت ضوابط زیست‌محیطی | مهندسان محیط‌زیست | بازرسان و کارشناسان بررسی علل حریق | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | کاردان‌ها و تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | متخصصان پزشکی اجتماعی و طب پیشگیری</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>آموزش و پرورش | ایمنی و امنیت عمومی | حقوق و امور دولتی | مهندسی و فناوری | مکانیک | شیمی</t>
+          <t>آموزش و پرورش | ایمنی و امنیت عمومی | قانون و دولت | مهندسی و فناوری | مکانیک | شیمی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>بازرسان ساختمان و سازه | بازرسان انطباق با مقررات زیست‌محیطی | کارشناسان و تکنسین‌های علوم محیطی و حفاظت، شامل بهداشت | مهندسان پیشگیری و حفاظت در برابر حریق | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معادن | کارشناسان بهداشت حرفه‌ای و ایمنی کار | پزشکان طب کار و پزشکی پیشگیری</t>
+          <t>بازرسان ساخت‌وساز و ساختمان | بازرسان رعایت ضوابط زیست‌محیطی | تکنسین‌های علوم و بهداشت محیط زیست | مهندسان پیشگیری و حفاظت از حریق | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | کارشناسان بهداشت حرفه‌ای و ایمنی کار | متخصصان پزشکی اجتماعی و طب پیشگیری</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | تفکر انتقادی | نظارت | نگارش | درک مطلب | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | نظارت | نگارش | درک مطلب | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | آموزش و پرورش | خدمات مشتریان و خدمات فردی | جامعه‌شناسی و مردم‌شناسی | پزشکی و دندان‌پزشکی</t>
+          <t>درمان و مشاوره | روان‌شناسی | آموزش و پرورش | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>پرستاران تخصصی روان‌پزشکی | مددکاران اجتماعی کودک، خانواده و مدرسه | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | تکنسین‌های روان‌پزشکی | روان‌پزشکان | مشاوران توانبخشی</t>
+          <t>پرستاران تخصصی روانپزشکی | مددکاران اجتماعی کودک، خانواده و مدرسه | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | تکنسین‌های روان‌پزشکی و بهداشت روان | روان‌پزشکان | مشاوران توانبخشی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | درمان و مشاوره | آموزش و پرورش | روان‌شناسی | امور دفتری و اداری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | درمان و مشاوره | آموزش و پرورش | روان‌شناسی | اداری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مدیران اداری و آموزشی مدارس | کارشناسان برنامه‌ریزی درسی و آموزشی | مشاوران سلامت روان | مشاوران توانبخشی | روان‌شناسان مدرسه | کارشناسان آموزش و توانمندسازی منابع انسانی</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مدیران آموزشی مقاطع ابتدایی و متوسطه | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مشاوران سلامت روان | مشاوران توانبخشی | روان‌شناسان مدارس | کارشناسان آموزش و توسعه منابع انسانی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نگارش | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | نگارش | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | خدمات مشتریان و خدمات فردی | جامعه‌شناسی و مردم‌شناسی | حقوق و امور دولتی | فلسفه و الهیات</t>
+          <t>درمان و مشاوره | روان‌شناسی | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | قانون و دولت | فلسفه و الهیات</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاور | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | روان‌پزشکان | روان‌شناسان مدرسه | مشاوران اعتیاد و اختلالات رفتاری</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاوران سلامت روان | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | روان‌پزشکان | روان‌شناسان مدارس | مشاوران اعتیاد و اختلالات رفتاری</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | خدمات مشتریان و خدمات فردی | جامعه‌شناسی و مردم‌شناسی | آموزش و پرورش | امور دفتری و اداری</t>
+          <t>درمان و مشاوره | روان‌شناسی | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | اداری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاور | مددکاران اجتماعی بخش سلامت و درمان | درمانگران ازدواج و خانواده | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | روان‌پزشکان | مشاوران اعتیاد و اختلالات رفتاری</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاوران سلامت روان | مددکاران اجتماعی بخش سلامت و درمان | درمانگران ازدواج و خانواده | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | روان‌پزشکان | مشاوران اعتیاد و اختلالات رفتاری</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,12 +850,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | درمان و مشاوره | روان‌شناسی | آموزش و پرورش | جامعه‌شناسی و مردم‌شناسی | امور کارکنان و منابع انسانی</t>
+          <t>خدمات مشتری و شخصی | درمان و مشاوره | روان‌شناسی | آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>روان‌شناسان بالینی و مشاور | مشاوران تحصیلی، شغلی و هدایت استعدادها | مددکاران اجتماعی بخش سلامت و درمان | مشاوران سلامت روان | کاردرمانگران | کارشناسان تفریح‌درمانی | دستیاران و کاردان‌های خدمات اجتماعی و انسانی</t>
+          <t>روان‌شناسان بالینی و مشاوران سلامت روان | مشاوران تحصیلی، شغلی و هدایت استعدادها | مددکاران اجتماعی بخش سلامت و درمان | مشاوران سلامت روان | کاردرمانگران | کارشناسان تفریح‌درمانی | دستیاران خدمات اجتماعی و انسانی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | خدمات مشتریان و خدمات فردی | جامعه‌شناسی و مردم‌شناسی | آموزش و پرورش | حقوق و امور دولتی</t>
+          <t>درمان و مشاوره | روان‌شناسی | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | قانون و دولت</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مشاوران اعتیاد و اختلالات رفتاری | مشاوران تحصیلی، شغلی و هدایت استعدادها | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مشاوران توانبخشی | مددکاران اجتماعی کودک، خانواده و مدرسه | دستیاران و کاردان‌های خدمات اجتماعی و انسانی</t>
+          <t>مشاوران اعتیاد و اختلالات رفتاری | مشاوران تحصیلی، شغلی و هدایت استعدادها | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مشاوران توانبخشی | مددکاران اجتماعی کودک، خانواده و مدرسه | دستیاران خدمات اجتماعی و انسانی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | روان‌شناسی | درمان و مشاوره | جامعه‌شناسی و مردم‌شناسی | آموزش و پرورش | حقوق و امور دولتی</t>
+          <t>خدمات مشتری و شخصی | روان‌شناسی | درمان و مشاوره | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | قانون و دولت</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>روان‌شناسان بالینی و مشاور | مشاوران تحصیلی، شغلی و هدایت استعدادها | مددکاران اجتماعی بخش سلامت و درمان | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | روان‌شناسان مدرسه | دستیاران و کاردان‌های خدمات اجتماعی و انسانی</t>
+          <t>روان‌شناسان بالینی و مشاوران سلامت روان | مشاوران تحصیلی، شغلی و هدایت استعدادها | مددکاران اجتماعی بخش سلامت و درمان | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | روان‌شناسان مدارس | دستیاران خدمات اجتماعی و انسانی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | تفکر انتقادی | شنیدن فعال | درک مطلب | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>سخن گفتن | تفکر انتقادی | گوش دادن فعال | درک مطلب | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>روان‌شناسی | درمان و مشاوره | جامعه‌شناسی و مردم‌شناسی | خدمات مشتریان و خدمات فردی | آموزش و پرورش | امور دفتری و اداری</t>
+          <t>روان‌شناسی | درمان و مشاوره | جامعه‌شناسی و انسان‌شناسی | خدمات مشتری و شخصی | آموزش و پرورش | اداری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاور | کارشناسان آموزش و ارتقای سلامت | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | مشاوران توانبخشی | دستیاران و کاردان‌های خدمات اجتماعی و انسانی</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاوران سلامت روان | کارشناسان آموزش بهداشت و ارتقای سلامت | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | مشاوران توانبخشی | دستیاران خدمات اجتماعی و انسانی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
